--- a/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
@@ -1233,12 +1233,52 @@
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bearing_stratum_embedment</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Bearing-stratum embedment</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>The as-built depth to which the element penetrates its designated bearing stratum, measured against the minimum embedment the design requires. Commonly expressed as a multiple of the element diameter, in which case the criterion's basis is per_diameter and baseLength carries the diameter.</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="G7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
         <v/>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>method_applicability</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Design-method applicability</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Whether the geometry and stiffness ratios of the as-designed layout fall within the range over which the chosen arching or load-transfer method's unit-cell idealisation is valid. The ratios themselves are carried by diggs:RITreatedAreaDesignType/methodApplicabilityRatio; this code names the pass/fail gate evaluated against them, so the verdict is a conformance criterion rather than a further ratio.</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
       </c>
       <c r="G8" s="9" t="n"/>
     </row>
@@ -1708,14 +1748,32 @@
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>bearing_stratum_embedment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
         <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>method_applicability</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">

--- a/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
@@ -1287,22 +1287,63 @@
         <f>IF(ISNA(VLOOKUP(B9,AssociatedElements!B$2:B2947,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>minimum_spacing_to_fresh_element</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Minimum spacing to a fresh element</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>The minimum plan distance permitted between an element being installed and a previously installed element that has not yet reached the age or strength at which it is unaffected by the installation. Controls installation effects - ground displacement, vibration and fresh concrete disturbance - on neighbours placed shortly before. Stated as a length; where a specification expresses it as a multiple of element diameter, the limit is the product of that multiple and the design diameter.</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
         <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>minimum_age_before_adjacent_installation</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Minimum age before adjacent installation</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>The minimum elapsed time between completing one element and beginning installation of an adjacent element, so that the earlier element has gained enough strength to be undisturbed. The time-based companion to minimum_spacing_to_fresh_element: a specification typically states one, the other, or both, and together they are what an installation sequence is designed to satisfy.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F10" s="13" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
@@ -1780,14 +1821,32 @@
         <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>minimum_spacing_to_fresh_element</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>minimum_age_before_adjacent_installation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">

--- a/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
@@ -1350,24 +1350,64 @@
         <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>penetration_rate</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Penetration rate</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>The rate at which the installation tool advances into the ground, as a design property a conformance criterion may govern. The design-side counterpart of mwd_properties.xml#penetration_rate, which names the same quantity as MEASURED during drilling; this entry names it as the subject of a requirement. Together with torque it is the pair a drilling refusal rule is normally written on, and such a rule is conjunctive - see diggs:CompositeAcceptanceCriterion.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
         <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="13" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>torque</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>The rotational force applied to the installation tool, as a design property a conformance criterion may govern. The design-side counterpart of mwd_properties.xml#torque, which names the same quantity as MEASURED during drilling. Paired with penetration_rate in a refusal criterion: neither alone defines refusal, which is why the combination is stated as a diggs:CompositeAcceptanceCriterion rather than left implicit in two co-scoped criteria.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F12" s="13" t="n"/>
-      <c r="G12" s="9" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
@@ -1853,14 +1893,32 @@
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>penetration_rate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
         <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B12" s="20" t="n"/>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>torque</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">

--- a/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/designProperty.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>The as-built inclination of the element from vertical (or from its designed batter), measured against its design tolerance.</t>
+          <t>The as-built inclination of the element from vertical (or from its designed batter), measured against its design tolerance. THE SPECIAL CASE OF alignment_deviation IN WHICH THE INTENDED ALIGNMENT IS VERTICAL, which is always so for rigid inclusion columns. Use alignment_deviation instead for an element intended to be raked, where a tolerance measured from vertical would be dominated by the design rake rather than by construction error. Judged against the alignmentDeviation property of diggs:AbstractLinearSamplingFeatureType (VERT1).</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1414,12 +1414,32 @@
         <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="13" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>alignment_deviation</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Alignment deviation</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>A tolerance on how far the constructed element may depart from its INTENDED alignment, judged against the alignmentDeviation property of diggs:AbstractLinearSamplingFeatureType. Dimensionless - a ratio in Euc or a percentage in %, the same quantity in two uoms, so a 1:100 tolerance is 0.01 Euc or 1 %. USE THIS RATHER THAN verticality WHERE THE ELEMENT IS NOT INTENDED TO BE VERTICAL - a raked grout hole or a battered pile, whose tolerance governs construction error about the design rake and not departure from vertical. The two terms are the same measurement against different datums: verticality is the special case of this one where the intended alignment is vertical, which is always true of rigid inclusion columns. Both are retained because a specification that says 'verticality tolerance 1:100' should be transcribable in the words it uses. Built at VERT1.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F13" s="13" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
@@ -1925,7 +1945,16 @@
         <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B13" s="20" t="n"/>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>alignment_deviation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>//diggs:DesignConformanceCriterion/diggs:designProperty</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
